--- a/package-output-map.xlsx
+++ b/package-output-map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/floswald/git/JPEtemplate/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/econ0763/Downloads/JPE/JPE-Jeenas-20240482/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067DD2C7-24FE-2447-A5A8-8F6542C7C06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D29C3ABE-6B40-2947-8941-A6DB4DA93F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="21900" windowHeight="12060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="26860" windowHeight="12060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="197">
   <si>
     <t>Data Preparation Program</t>
   </si>
@@ -46,6 +46,576 @@
   </si>
   <si>
     <t>In-text numbers</t>
+  </si>
+  <si>
+    <t>code/Python/cleaning/CS_cleaning_code.py:41</t>
+  </si>
+  <si>
+    <t>proprietary-data-not-for-publication/processed/CS_data_clean.csv</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>code/Python/cleaning/CRSP_cleaning_code.py:29</t>
+  </si>
+  <si>
+    <t>proprietary-data-not-for-publication/processed/CRSP_split/CRSP_data_clean_X.csv</t>
+  </si>
+  <si>
+    <t>code/Python/cleaning/CStoCRSP_merge.py:145</t>
+  </si>
+  <si>
+    <t>proprietary-data-not-for-publication/processed/CRSP_split/CRSP_data_DD_int_X.csv</t>
+  </si>
+  <si>
+    <t>code/Python/cleaning/CRSP_par_prep.py:50</t>
+  </si>
+  <si>
+    <t>proprietary-data-not-for-publication/processed/CRSP_split/CRSP_data_DD_int_forpar_X.csv</t>
+  </si>
+  <si>
+    <t>code/Python/DD_work_run.py:208</t>
+  </si>
+  <si>
+    <t>proprietary-data-not-for-publication/processed/CRSP_split/CRSP_data_DD_int_done_X.csv</t>
+  </si>
+  <si>
+    <t>code/Python/cleaning/Wscope_compile_code.py:57</t>
+  </si>
+  <si>
+    <t>proprietary-data-not-for-publication/processed/Wscope_data_compiled.csv</t>
+  </si>
+  <si>
+    <t>code/Python/Micro_reg_prep_code.py:250</t>
+  </si>
+  <si>
+    <t>proprietary-data-not-for-publication/processed/Micro_reg_data_compiled.csv</t>
+  </si>
+  <si>
+    <t>code/R/Micro_reg_code.r:187</t>
+  </si>
+  <si>
+    <t>proprietary-data-not-for-publication/processed/p_data_saved.rds</t>
+  </si>
+  <si>
+    <t>code/R/Micro_reg_code.r:242</t>
+  </si>
+  <si>
+    <t>interim_output/CS_agg_cheat_t.csv</t>
+  </si>
+  <si>
+    <t>code/R/Micro_reg_code.r:777</t>
+  </si>
+  <si>
+    <t>interim_output/emp_dissreg_vals_ind(X)_dep(Y).csv</t>
+  </si>
+  <si>
+    <t>code/R/Micro_reg_code.r:1096</t>
+  </si>
+  <si>
+    <t>interim_output/Fig4b_nums_groupspec_Dfreq.txt</t>
+  </si>
+  <si>
+    <t>code/R/Micro_reg_code.r:1607-1608</t>
+  </si>
+  <si>
+    <t>interim_output/Fig*_slevsbetas_vec_q_vals/cis(...).csv</t>
+  </si>
+  <si>
+    <t>code/Python/FOFA_analysis_code.py:117</t>
+  </si>
+  <si>
+    <t>interim_output/FOFA_agg_cheat_t.csv</t>
+  </si>
+  <si>
+    <t>code/R/Micro_model_reg_code.r:312</t>
+  </si>
+  <si>
+    <t>interim_output/mod_dissreg_vals_dep(Y).csv</t>
+  </si>
+  <si>
+    <t>code/Julia/Julia_model_code/Master_model_work.jl:470</t>
+  </si>
+  <si>
+    <t>interim_output/model_interim_output/df_model_panel.csv</t>
+  </si>
+  <si>
+    <t>code/Julia/Julia_model_code/Master_model_work.jl:583</t>
+  </si>
+  <si>
+    <t>interim_output/model_interim_output/IRFs_base.csv</t>
+  </si>
+  <si>
+    <t>interim_output/model_interim_output/savedout/*.txt and savedsolns/*.jld checkpoint files</t>
+  </si>
+  <si>
+    <t>Reproduced</t>
+  </si>
+  <si>
+    <t>Figure 1 (Fig1a, Fig1b)</t>
+  </si>
+  <si>
+    <t>code/R/Micro_reg_code.r</t>
+  </si>
+  <si>
+    <t>404, 415, 425</t>
+  </si>
+  <si>
+    <t>Figure 2 (Fig2a-Fig2c)</t>
+  </si>
+  <si>
+    <t>code/R/Micro_eventstudy_plottr.r</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>Figure 3 (Fig3a, Fig3b)</t>
+  </si>
+  <si>
+    <t>1387</t>
+  </si>
+  <si>
+    <t>Figure 4 (Fig4a, Fig4b)</t>
+  </si>
+  <si>
+    <t>code/Julia/Julia_model_code/Master_model_work.jl</t>
+  </si>
+  <si>
+    <t>280, 431</t>
+  </si>
+  <si>
+    <t>Figure 5</t>
+  </si>
+  <si>
+    <t>579</t>
+  </si>
+  <si>
+    <t>Figure 6</t>
+  </si>
+  <si>
+    <t>code/Julia/Julia_model_code/auxiliary_model_functions.jl</t>
+  </si>
+  <si>
+    <t>2487</t>
+  </si>
+  <si>
+    <t>Figure 7 (Fig7a, Fig7b)</t>
+  </si>
+  <si>
+    <t>1104, 1127</t>
+  </si>
+  <si>
+    <t>Figure 8 (Fig8a, Fig8b)</t>
+  </si>
+  <si>
+    <t>1161, 1171</t>
+  </si>
+  <si>
+    <t>Table 1</t>
+  </si>
+  <si>
+    <t>746</t>
+  </si>
+  <si>
+    <t>Table 2</t>
+  </si>
+  <si>
+    <t>831</t>
+  </si>
+  <si>
+    <t>Figure A.1</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>Table A.1</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>Table A.2</t>
+  </si>
+  <si>
+    <t>517</t>
+  </si>
+  <si>
+    <t>Table A.3</t>
+  </si>
+  <si>
+    <t>612</t>
+  </si>
+  <si>
+    <t>Table A.4</t>
+  </si>
+  <si>
+    <t>679</t>
+  </si>
+  <si>
+    <t>Figure A.2 (FigA2a-FigA2c)</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>Figure A.3 (FigA3a-FigA3c)</t>
+  </si>
+  <si>
+    <t>Figure A.4 (FigA4a-FigA4c)</t>
+  </si>
+  <si>
+    <t>Figure A.5 (FigA5a, FigA5b)</t>
+  </si>
+  <si>
+    <t>1387, 1922</t>
+  </si>
+  <si>
+    <t>Figure A.6 (FigA6a-FigA6d)</t>
+  </si>
+  <si>
+    <t>Figure A.7 (FigA7a, FigA7b)</t>
+  </si>
+  <si>
+    <t>Figure A.8 (FigA8a, FigA8b)</t>
+  </si>
+  <si>
+    <t>Figure A.9 (FigA9a, FigA9b)</t>
+  </si>
+  <si>
+    <t>Figure A.10 (FigA10a, FigA10b)</t>
+  </si>
+  <si>
+    <t>1405</t>
+  </si>
+  <si>
+    <t>Figure A.11 (FigA11a, FigA11b)</t>
+  </si>
+  <si>
+    <t>Figure A.12 (FigA12a, FigA12b)</t>
+  </si>
+  <si>
+    <t>1387, 1756</t>
+  </si>
+  <si>
+    <t>Figure A.13 (FigA13a, FigA13b)</t>
+  </si>
+  <si>
+    <t>1756</t>
+  </si>
+  <si>
+    <t>Figure A.14 (FigA14a, FigA14b)</t>
+  </si>
+  <si>
+    <t>2212, 2237</t>
+  </si>
+  <si>
+    <t>Table A.5</t>
+  </si>
+  <si>
+    <t>code/Python/FOFA_analysis_code.py</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>Figure A.15 (FigA15a-FigA15d)</t>
+  </si>
+  <si>
+    <t>code/MATLAB/LPAgg_main.m</t>
+  </si>
+  <si>
+    <t>183, 205, 227, 250</t>
+  </si>
+  <si>
+    <t>Table B.1 (manual table from components)</t>
+  </si>
+  <si>
+    <t>code/Julia/Julia_empirics_code/BDS_analysis_code.jl; code/R/Micro_reg_code.r; code/Julia/Julia_model_code/Master_model_work.jl</t>
+  </si>
+  <si>
+    <t>40; 218; 204</t>
+  </si>
+  <si>
+    <t>Table B.2</t>
+  </si>
+  <si>
+    <t>code/Python/Generate_TabB2.py</t>
+  </si>
+  <si>
+    <t>15, 60</t>
+  </si>
+  <si>
+    <t>Table B.3</t>
+  </si>
+  <si>
+    <t>code/R/Micro_model_reg_code.r</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>Table B.4</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>Table B.5 (manual table from component)</t>
+  </si>
+  <si>
+    <t>code/Julia/Julia_model_code/calib_functions.jl</t>
+  </si>
+  <si>
+    <t>392</t>
+  </si>
+  <si>
+    <t>Figure B.1</t>
+  </si>
+  <si>
+    <t>338</t>
+  </si>
+  <si>
+    <t>Figure B.2</t>
+  </si>
+  <si>
+    <t>2514</t>
+  </si>
+  <si>
+    <t>Figure B.3 (FigB3a, FigB3b)</t>
+  </si>
+  <si>
+    <t>2585, 2648</t>
+  </si>
+  <si>
+    <t>Figure B.4</t>
+  </si>
+  <si>
+    <t>2526</t>
+  </si>
+  <si>
+    <t>Figure B.5</t>
+  </si>
+  <si>
+    <t>1088</t>
+  </si>
+  <si>
+    <t>Figure B.6</t>
+  </si>
+  <si>
+    <t>690</t>
+  </si>
+  <si>
+    <t>Figure B.7</t>
+  </si>
+  <si>
+    <t>738</t>
+  </si>
+  <si>
+    <t>Figure B.8</t>
+  </si>
+  <si>
+    <t>1146</t>
+  </si>
+  <si>
+    <t>Figure B.9</t>
+  </si>
+  <si>
+    <t>1330</t>
+  </si>
+  <si>
+    <t>Figure B.10</t>
+  </si>
+  <si>
+    <t>Figure B.11 (FigB11a, FigB11b)</t>
+  </si>
+  <si>
+    <t>code/Julia/Julia_model_code/auxiliary_model_functions.jl; code/Julia/Julia_model_code/Master_model_work.jl</t>
+  </si>
+  <si>
+    <t>2492; 1245</t>
+  </si>
+  <si>
+    <t>Figure B.12</t>
+  </si>
+  <si>
+    <t>1457</t>
+  </si>
+  <si>
+    <t>Figure B.13 (FigB13a, FigB13b)</t>
+  </si>
+  <si>
+    <t>2495; 1574</t>
+  </si>
+  <si>
+    <t>Figure B.14 (FigB14a, FigB14b)</t>
+  </si>
+  <si>
+    <t>1474, 1590</t>
+  </si>
+  <si>
+    <t>Footnote 3</t>
+  </si>
+  <si>
+    <t>258, 313</t>
+  </si>
+  <si>
+    <t>Footnote 15</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>Footnote 46</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>Section 4.2 text</t>
+  </si>
+  <si>
+    <t>288</t>
+  </si>
+  <si>
+    <t>Section 5.1 text</t>
+  </si>
+  <si>
+    <t>671</t>
+  </si>
+  <si>
+    <t>Section 5.2 text</t>
+  </si>
+  <si>
+    <t>1188, 1212, 1332</t>
+  </si>
+  <si>
+    <t>Footnote 57</t>
+  </si>
+  <si>
+    <t>1220</t>
+  </si>
+  <si>
+    <t>Appendix A.2 text</t>
+  </si>
+  <si>
+    <t>520</t>
+  </si>
+  <si>
+    <t>Footnote 61</t>
+  </si>
+  <si>
+    <t>791</t>
+  </si>
+  <si>
+    <t>Footnote 74</t>
+  </si>
+  <si>
+    <t>327</t>
+  </si>
+  <si>
+    <t>Appendix B.5.3 text</t>
+  </si>
+  <si>
+    <t>372</t>
+  </si>
+  <si>
+    <t>Footnote 87</t>
+  </si>
+  <si>
+    <t>345</t>
+  </si>
+  <si>
+    <t>Appendix B.10.1 text</t>
+  </si>
+  <si>
+    <t>code/Python/FOFA_analysis_code.py; code/Python/TB3_analysis_code.py</t>
+  </si>
+  <si>
+    <t>111; 29</t>
+  </si>
+  <si>
+    <t>Appendix B.11.1 text</t>
+  </si>
+  <si>
+    <t>495</t>
+  </si>
+  <si>
+    <t>Appendix B.11.2 text</t>
+  </si>
+  <si>
+    <t>1616</t>
+  </si>
+  <si>
+    <t>code/Julia/Julia_model_code/auxiliary_model_functions.jl:534</t>
+  </si>
+  <si>
+    <t>No, different</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Linked generated Section 4.2 numbers differ from paper: saved 0.52-&gt;0.23 and 0.41-&gt;0.36; paper reports 0.53-&gt;0.24 and 0.43-&gt;0.39.</t>
+  </si>
+  <si>
+    <t>Saved Table 2 model values differ from paper: pre model 13.65, -0.053, 0.769 vs paper 14.73, -0.049, 0.793; post -0.060, 0.931 vs paper -0.059, 0.953.</t>
+  </si>
+  <si>
+    <t>Model calibration components differ: saved freq(D=1)=0.255 and E[n0]/E[n]=0.26; paper reports 0.252 and 0.25.</t>
+  </si>
+  <si>
+    <t>Model column differs in several untargeted moments, e.g. saved -0.231, 0.122, 0.046, 0.054, 0.017, 0.236, 0.273 vs paper -0.228, 0.125, 0.049, 0.061, 0.014, 0.221, 0.283.</t>
+  </si>
+  <si>
+    <t>Saved model regression table differs from paper in coefficients and observations, e.g. leverage first row 0.364/0.184/0.310 vs paper 0.351/0.169/0.292.</t>
+  </si>
+  <si>
+    <t>Saved model R2 table differs from paper, e.g. leverage 0.73/0.08/0.53 vs paper 0.70/0.07/0.49; liquidity 0.80/0.71/0.57 vs paper 0.95/0.80/0.69.</t>
+  </si>
+  <si>
+    <t>Table component differs slightly: saved liquidity public-private difference 0.047; paper reports 0.048.</t>
+  </si>
+  <si>
+    <t>Linked isolated liquid-asset-return-shock text differs: saved -0.43% pre and -0.57% post; paper reports -0.47% and -0.60%.</t>
+  </si>
+  <si>
+    <t>Linked Appendix B.11.2 decomposition text differs: saved Q share about 3/5 and rb+rm about 2/5; paper reports Q about 2/5 and rb+rm about 3/5.</t>
+  </si>
+  <si>
+    <t>Model line below the one in paper</t>
+  </si>
+  <si>
+    <t>Panel b differs</t>
+  </si>
+  <si>
+    <t>Post-90 differs; Linked Section 5.2 auxiliary numbers differ: saved rm/rb peak ratio 0.26 pre and 0.47 post, GE-PE Q share 1.05; paper reports about 1/3 to 1/2 and about 2/3 Q share.</t>
+  </si>
+  <si>
+    <t>Panel a differs slightly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Differs slightly </t>
+  </si>
+  <si>
+    <t>Replicated 0.52-&gt;0.23 and 0.41-&gt;0.36; paper reports 0.53-&gt;0.24 and 0.43-&gt;0.39.</t>
+  </si>
+  <si>
+    <t>Replicated aggregate debt-to-capital changes by -0.002, roughly -0.2pp; paper says only 0.1pp.</t>
+  </si>
+  <si>
+    <t>Replicated rm/rb peak ratio 0.26 pre and 0.47 post vs about 1/3 to 1/2 in paper; GE-PE Q share 1.05 vs about 2/3 in paper; isolated rm shock -0.43/-0.57 vs -0.47/-0.60.</t>
+  </si>
+  <si>
+    <t>Replicated footnote value is 4.5% of net worth; paper footnote reports about 4.4%.</t>
+  </si>
+  <si>
+    <t>Replicated mean b/k 0.294 and BA-BN 0.281, elasticities 0.144/-0.134; paper reports about 0.31, 0.296, and 0.204/-0.113.</t>
+  </si>
+  <si>
+    <t>Replicated Q share about 3/5 and rb+rm about 2/5; paper reports Q about 2/5 and rb+rm about 3/5.</t>
   </si>
 </sst>
 </file>
@@ -89,13 +659,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -104,7 +671,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -434,19 +1012,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E86"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.5" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="52.1640625" customWidth="1"/>
+    <col min="2" max="2" width="86" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -456,56 +1029,1234 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
+      <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+      <c r="D20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" t="s">
+        <v>175</v>
+      </c>
+      <c r="E24" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" t="s">
+        <v>175</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" t="s">
+        <v>175</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28" t="s">
+        <v>175</v>
+      </c>
+      <c r="E28" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" t="s">
+        <v>175</v>
+      </c>
+      <c r="E30" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D51" t="s">
+        <v>175</v>
+      </c>
+      <c r="E51" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D52" t="s">
+        <v>175</v>
+      </c>
+      <c r="E52" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D53" t="s">
+        <v>175</v>
+      </c>
+      <c r="E53" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54" t="s">
+        <v>175</v>
+      </c>
+      <c r="E54" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D55" t="s">
+        <v>175</v>
+      </c>
+      <c r="E55" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D59" t="s">
+        <v>175</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D60" t="s">
+        <v>175</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D64" t="s">
+        <v>175</v>
+      </c>
+      <c r="E64" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D69" t="s">
+        <v>175</v>
+      </c>
+      <c r="E69" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B71" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C71" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>2</v>
+      <c r="D71" t="s">
+        <v>41</v>
+      </c>
+      <c r="E71" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D75" t="s">
+        <v>175</v>
+      </c>
+      <c r="E75" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D76" t="s">
+        <v>175</v>
+      </c>
+      <c r="E76" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D77" t="s">
+        <v>175</v>
+      </c>
+      <c r="E77" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D78" t="s">
+        <v>175</v>
+      </c>
+      <c r="E78" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D82" t="s">
+        <v>175</v>
+      </c>
+      <c r="E82" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D86" t="s">
+        <v>175</v>
+      </c>
+      <c r="E86" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D86" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="D1:D54 E30 E51:E54 D55:E55 D56:D1048576 E58 E68">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="No">
+      <formula>NOT(ISERROR(SEARCH("No",D1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <ignoredErrors>
+    <ignoredError sqref="C85" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/package-output-map.xlsx
+++ b/package-output-map.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/econ0763/Downloads/JPE/JPE-Jeenas-20240482/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D29C3ABE-6B40-2947-8941-A6DB4DA93F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A4EF06-592D-2F47-B06E-7E9895827F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="26860" windowHeight="12060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="175">
   <si>
     <t>Data Preparation Program</t>
   </si>
@@ -550,72 +550,6 @@
   </si>
   <si>
     <t>code/Julia/Julia_model_code/auxiliary_model_functions.jl:534</t>
-  </si>
-  <si>
-    <t>No, different</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Linked generated Section 4.2 numbers differ from paper: saved 0.52-&gt;0.23 and 0.41-&gt;0.36; paper reports 0.53-&gt;0.24 and 0.43-&gt;0.39.</t>
-  </si>
-  <si>
-    <t>Saved Table 2 model values differ from paper: pre model 13.65, -0.053, 0.769 vs paper 14.73, -0.049, 0.793; post -0.060, 0.931 vs paper -0.059, 0.953.</t>
-  </si>
-  <si>
-    <t>Model calibration components differ: saved freq(D=1)=0.255 and E[n0]/E[n]=0.26; paper reports 0.252 and 0.25.</t>
-  </si>
-  <si>
-    <t>Model column differs in several untargeted moments, e.g. saved -0.231, 0.122, 0.046, 0.054, 0.017, 0.236, 0.273 vs paper -0.228, 0.125, 0.049, 0.061, 0.014, 0.221, 0.283.</t>
-  </si>
-  <si>
-    <t>Saved model regression table differs from paper in coefficients and observations, e.g. leverage first row 0.364/0.184/0.310 vs paper 0.351/0.169/0.292.</t>
-  </si>
-  <si>
-    <t>Saved model R2 table differs from paper, e.g. leverage 0.73/0.08/0.53 vs paper 0.70/0.07/0.49; liquidity 0.80/0.71/0.57 vs paper 0.95/0.80/0.69.</t>
-  </si>
-  <si>
-    <t>Table component differs slightly: saved liquidity public-private difference 0.047; paper reports 0.048.</t>
-  </si>
-  <si>
-    <t>Linked isolated liquid-asset-return-shock text differs: saved -0.43% pre and -0.57% post; paper reports -0.47% and -0.60%.</t>
-  </si>
-  <si>
-    <t>Linked Appendix B.11.2 decomposition text differs: saved Q share about 3/5 and rb+rm about 2/5; paper reports Q about 2/5 and rb+rm about 3/5.</t>
-  </si>
-  <si>
-    <t>Model line below the one in paper</t>
-  </si>
-  <si>
-    <t>Panel b differs</t>
-  </si>
-  <si>
-    <t>Post-90 differs; Linked Section 5.2 auxiliary numbers differ: saved rm/rb peak ratio 0.26 pre and 0.47 post, GE-PE Q share 1.05; paper reports about 1/3 to 1/2 and about 2/3 Q share.</t>
-  </si>
-  <si>
-    <t>Panel a differs slightly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Differs slightly </t>
-  </si>
-  <si>
-    <t>Replicated 0.52-&gt;0.23 and 0.41-&gt;0.36; paper reports 0.53-&gt;0.24 and 0.43-&gt;0.39.</t>
-  </si>
-  <si>
-    <t>Replicated aggregate debt-to-capital changes by -0.002, roughly -0.2pp; paper says only 0.1pp.</t>
-  </si>
-  <si>
-    <t>Replicated rm/rb peak ratio 0.26 pre and 0.47 post vs about 1/3 to 1/2 in paper; GE-PE Q share 1.05 vs about 2/3 in paper; isolated rm shock -0.43/-0.57 vs -0.47/-0.60.</t>
-  </si>
-  <si>
-    <t>Replicated footnote value is 4.5% of net worth; paper footnote reports about 4.4%.</t>
-  </si>
-  <si>
-    <t>Replicated mean b/k 0.294 and BA-BN 0.281, elasticities 0.144/-0.134; paper reports about 0.31, 0.296, and 0.204/-0.113.</t>
-  </si>
-  <si>
-    <t>Replicated Q share about 3/5 and rb+rm about 2/5; paper reports Q about 2/5 and rb+rm about 3/5.</t>
   </si>
 </sst>
 </file>
@@ -1257,9 +1191,6 @@
       <c r="D20" t="s">
         <v>41</v>
       </c>
-      <c r="E20" t="s">
-        <v>176</v>
-      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
@@ -1313,11 +1244,8 @@
       <c r="C24" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D24" t="s">
-        <v>175</v>
-      </c>
-      <c r="E24" t="s">
-        <v>177</v>
+      <c r="D24" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -1344,12 +1272,10 @@
       <c r="C26" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D26" t="s">
-        <v>175</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>186</v>
-      </c>
+      <c r="D26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="2"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
@@ -1361,12 +1287,10 @@
       <c r="C27" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D27" t="s">
-        <v>175</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>187</v>
-      </c>
+      <c r="D27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
@@ -1378,11 +1302,8 @@
       <c r="C28" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D28" t="s">
-        <v>175</v>
-      </c>
-      <c r="E28" t="s">
-        <v>188</v>
+      <c r="D28" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -1409,11 +1330,8 @@
       <c r="C30" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D30" t="s">
-        <v>175</v>
-      </c>
-      <c r="E30" t="s">
-        <v>178</v>
+      <c r="D30" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -1706,11 +1624,8 @@
       <c r="C51" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D51" t="s">
-        <v>175</v>
-      </c>
-      <c r="E51" t="s">
-        <v>179</v>
+      <c r="D51" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
@@ -1723,11 +1638,8 @@
       <c r="C52" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D52" t="s">
-        <v>175</v>
-      </c>
-      <c r="E52" t="s">
-        <v>180</v>
+      <c r="D52" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
@@ -1740,11 +1652,8 @@
       <c r="C53" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D53" t="s">
-        <v>175</v>
-      </c>
-      <c r="E53" t="s">
-        <v>181</v>
+      <c r="D53" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
@@ -1757,11 +1666,8 @@
       <c r="C54" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D54" t="s">
-        <v>175</v>
-      </c>
-      <c r="E54" t="s">
-        <v>182</v>
+      <c r="D54" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
@@ -1774,11 +1680,8 @@
       <c r="C55" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D55" t="s">
-        <v>175</v>
-      </c>
-      <c r="E55" t="s">
-        <v>183</v>
+      <c r="D55" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
@@ -1820,11 +1723,9 @@
         <v>120</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>189</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="E58" s="2"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
@@ -1836,12 +1737,10 @@
       <c r="C59" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D59" t="s">
-        <v>175</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>190</v>
-      </c>
+      <c r="D59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" s="2"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
@@ -1853,12 +1752,10 @@
       <c r="C60" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D60" t="s">
-        <v>175</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>190</v>
-      </c>
+      <c r="D60" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" s="2"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
@@ -1912,11 +1809,8 @@
       <c r="C64" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D64" t="s">
-        <v>175</v>
-      </c>
-      <c r="E64" t="s">
-        <v>184</v>
+      <c r="D64" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
@@ -1972,11 +1866,9 @@
         <v>140</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>190</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="E68" s="2"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
@@ -1988,11 +1880,8 @@
       <c r="C69" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D69" t="s">
-        <v>175</v>
-      </c>
-      <c r="E69" t="s">
-        <v>185</v>
+      <c r="D69" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
@@ -2014,9 +1903,6 @@
       <c r="D71" t="s">
         <v>41</v>
       </c>
-      <c r="E71" t="s">
-        <v>176</v>
-      </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
@@ -2070,11 +1956,8 @@
       <c r="C75" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D75" t="s">
-        <v>175</v>
-      </c>
-      <c r="E75" t="s">
-        <v>191</v>
+      <c r="D75" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
@@ -2087,11 +1970,8 @@
       <c r="C76" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D76" t="s">
-        <v>175</v>
-      </c>
-      <c r="E76" t="s">
-        <v>192</v>
+      <c r="D76" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
@@ -2104,11 +1984,8 @@
       <c r="C77" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D77" t="s">
-        <v>175</v>
-      </c>
-      <c r="E77" t="s">
-        <v>193</v>
+      <c r="D77" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
@@ -2121,11 +1998,8 @@
       <c r="C78" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D78" t="s">
-        <v>175</v>
-      </c>
-      <c r="E78" t="s">
-        <v>194</v>
+      <c r="D78" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
@@ -2156,7 +2030,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>161</v>
       </c>
@@ -2170,7 +2044,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>163</v>
       </c>
@@ -2180,14 +2054,11 @@
       <c r="C82" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D82" t="s">
-        <v>175</v>
-      </c>
-      <c r="E82" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D82" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>165</v>
       </c>
@@ -2201,7 +2072,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>167</v>
       </c>
@@ -2215,7 +2086,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>170</v>
       </c>
@@ -2229,7 +2100,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>172</v>
       </c>
@@ -2239,16 +2110,13 @@
       <c r="C86" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D86" t="s">
-        <v>175</v>
-      </c>
-      <c r="E86" t="s">
-        <v>196</v>
+      <c r="D86" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D86" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="D1:D54 E30 E51:E54 D55:E55 D56:D1048576 E58 E68">
+  <conditionalFormatting sqref="E30 E51:E55 E58 E68 D1:D1048576">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",D1)))</formula>
     </cfRule>
